--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N98_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N98_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>49.73978555288096</v>
+        <v>8.082715152343157</v>
       </c>
       <c r="D2" t="n">
-        <v>49.74073707700168</v>
+        <v>8.082869775012774</v>
       </c>
       <c r="E2" t="n">
-        <v>12.48865204801166</v>
+        <v>2.029405957801894</v>
       </c>
       <c r="F2" t="n">
-        <v>13.58988645737596</v>
+        <v>2.208356549323593</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.80565953694956</v>
+        <v>5.655919674754304</v>
       </c>
       <c r="D3" t="n">
-        <v>34.72562559468854</v>
+        <v>5.642914159136888</v>
       </c>
       <c r="E3" t="n">
-        <v>12.48865204801166</v>
+        <v>2.029405957801894</v>
       </c>
       <c r="F3" t="n">
-        <v>13.58988645737596</v>
+        <v>2.208356549323593</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.7852567042095</v>
+        <v>5.652604214434044</v>
       </c>
       <c r="D4" t="n">
-        <v>34.79560474787831</v>
+        <v>5.654285771530225</v>
       </c>
       <c r="E4" t="n">
-        <v>12.48865204801166</v>
+        <v>2.029405957801894</v>
       </c>
       <c r="F4" t="n">
-        <v>13.58988645737596</v>
+        <v>2.208356549323593</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.67324498195332</v>
+        <v>7.584402309567414</v>
       </c>
       <c r="D5" t="n">
-        <v>46.5709294690267</v>
+        <v>7.567776038716839</v>
       </c>
       <c r="E5" t="n">
-        <v>12.48865204801166</v>
+        <v>2.029405957801894</v>
       </c>
       <c r="F5" t="n">
-        <v>13.58988645737596</v>
+        <v>2.208356549323593</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>20.29370530944034</v>
+        <v>3.297727112784055</v>
       </c>
       <c r="D6" t="n">
-        <v>20.37637991783691</v>
+        <v>3.311161736648498</v>
       </c>
       <c r="E6" t="n">
-        <v>12.48865204801166</v>
+        <v>2.029405957801894</v>
       </c>
       <c r="F6" t="n">
-        <v>13.58988645737596</v>
+        <v>2.208356549323593</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>43.78524662029787</v>
+        <v>7.115102575798404</v>
       </c>
       <c r="D7" t="n">
-        <v>43.87508575155715</v>
+        <v>7.129701434628037</v>
       </c>
       <c r="E7" t="n">
-        <v>12.48865204801166</v>
+        <v>2.029405957801894</v>
       </c>
       <c r="F7" t="n">
-        <v>13.58988645737596</v>
+        <v>2.208356549323593</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>20.17575241763249</v>
+        <v>3.27855976786528</v>
       </c>
       <c r="D8" t="n">
-        <v>20.0974586526491</v>
+        <v>3.265837031055478</v>
       </c>
       <c r="E8" t="n">
-        <v>12.48865204801166</v>
+        <v>2.029405957801894</v>
       </c>
       <c r="F8" t="n">
-        <v>13.58988645737596</v>
+        <v>2.208356549323593</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>51.36816199196017</v>
+        <v>8.347326323693528</v>
       </c>
       <c r="D9" t="n">
-        <v>51.46148036047044</v>
+        <v>8.362490558576447</v>
       </c>
       <c r="E9" t="n">
-        <v>12.48865204801166</v>
+        <v>2.029405957801894</v>
       </c>
       <c r="F9" t="n">
-        <v>13.58988645737596</v>
+        <v>2.208356549323593</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>11.43914160468387</v>
+        <v>1.858860510761129</v>
       </c>
       <c r="D10" t="n">
-        <v>11.48636955020568</v>
+        <v>1.866535051908424</v>
       </c>
       <c r="E10" t="n">
-        <v>12.48865204801166</v>
+        <v>2.029405957801894</v>
       </c>
       <c r="F10" t="n">
-        <v>13.58988645737596</v>
+        <v>2.208356549323593</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>34.77195191809545</v>
+        <v>5.65044218669051</v>
       </c>
       <c r="D11" t="n">
-        <v>22.27666940994546</v>
+        <v>3.619958779116138</v>
       </c>
       <c r="E11" t="n">
-        <v>12.48865204801166</v>
+        <v>2.029405957801894</v>
       </c>
       <c r="F11" t="n">
-        <v>13.58988645737596</v>
+        <v>2.208356549323593</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>29.41622247191349</v>
+        <v>4.780136151685943</v>
       </c>
       <c r="D12" t="n">
-        <v>18.66815470259447</v>
+        <v>3.033575139171602</v>
       </c>
       <c r="E12" t="n">
-        <v>12.48865204801166</v>
+        <v>2.029405957801894</v>
       </c>
       <c r="F12" t="n">
-        <v>13.58988645737596</v>
+        <v>2.208356549323593</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
